--- a/data/hero/2026_04/naver.xlsx
+++ b/data/hero/2026_04/naver.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="weekly" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="reviews" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="weekly" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reviews" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -36,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -44,12 +47,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -419,124 +431,124 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>url</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>appearances</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>total_weeks</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>avg_rank</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>best_rank</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>first_rank</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>last_rank</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>first_date</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>last_date</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rank_change</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>first_review</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>last_review</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>review_growth</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>review_growth_pct</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>avg_star</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>score_stability</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>score_best_rank</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>score_rank_change</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>score_engagement</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>total_score</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>url</t>
         </is>
       </c>
     </row>
@@ -557,64 +569,68 @@
       <c r="D2" t="n">
         <v>195000</v>
       </c>
-      <c r="E2" t="n">
-        <v>3</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/malldaewoong/products/12727841644</t>
+        </is>
       </c>
       <c r="F2" t="n">
         <v>3</v>
       </c>
       <c r="G2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2" t="n">
         <v>42.67</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>13</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>82</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>13</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>20260405</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>20260419</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>69</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>634</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>1026</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>392</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>61.83</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>4.9</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>30</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>25</v>
       </c>
-      <c r="V2" t="n">
+      <c r="W2" t="n">
         <v>20</v>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>76</v>
       </c>
-      <c r="X2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -631,32 +647,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>week</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>review</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>star</t>
         </is>
@@ -733,28 +749,7826 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>review_date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>rating</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>reviewer</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>content</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>26.04.20.</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ttta*****</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>중간고사 준비로 피곤해하는 고3 딸을위해 또 재재재구매합니다. 이번엔 샤인머스켓맛도 구매해봅니다. 맛있다고하네요.
+냉동실에 넣어 시원하게 먹는걸 좋아하네요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>26.04.19.</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>lbh0***</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>아이들이 시험기간이라서 먹는다해서
+구입했는데 먹기는 편리한데 맛은 쓰면서
+짜다네요</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>26.04.18.</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>rnld******</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>고등딸아이 반친구들이 다 먹고있다며
+대웅. 요제품을 보여주더라구요.
+대웅몰에서 당일배송해주셔서
+내일기숙사 복귀할때 챙겨줄 수있네요.
+효과만 최고면 좋겠어요.
+기대해봅니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>26.04.20.</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>mska*****</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>공부하는 아들이 늘 먹어요.... 근데 오리지널이 더 낫다고 하네요.... 샤인머스켓향은 다음에 사면 안될것같아요... ^^ 개인취향이니까... 처음으로 연두색 사봤는데... 다음엔 그냥 오렌지색만 사는걸로~ㅎㅎㅎ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>26.04.22.</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>chan*******</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>시험 보기 전 항상 먹이고는 있는데..크게 좋다라는건 못 느끼고 있어요~ㅋ 안 먹이는것 보단 났겠다 싶은 마음에..먹기 편하고 얼려서 먹기도 하고~ 저희 아이는 오렌지 맛이 더 맛있다네요!</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>26.04.22.</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ying*****</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>기존에 다른 제품 먹는데 똑떨어져서 사달라는데 성분이 좋은거 같아 제약회사 믿고 구매했어요 효과봄 좋겄네요</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>26.04.15.</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>hjym*********</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>물기없는 젤리같다고 하네요.
+먹기는 편한데 텁텁하고, 카페인성분이 있어서 그런지 목은 말라서 물을 자주 마셔야하고,
+효과는 짱이랍니다. 
+친구들도 먹고 있다고 먼저 먹어보고 싶다고 하길래커피보다 낫겠지 싶어서 사줬습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>26.04.19.</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>hye5***</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>요즘 아이들 중간고사 기간이라 재 구매했어요
+사람들 마다 다르겠지만 우리 아이들은 오렌지보다 샤인머스캣 맛이 더 맛있다고 하네요</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>26.04.02.</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1771******</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>아이가 집중력이 필요로 한 날은 말하지 않아도 알아서 챙겨가요.!  그동안 몸에 좋다는 비타민들은 한 통 다 먹기가 힘들었는데. 집중샷은 다 먹기도 전에 사야한다고 미리 요청까지 하니 아이가 효과를 느끼나 봅니다!!  
+샤인머스켓맛이 새로 나와서 같이 주문했는데, 아이는 샤인머스켓이 더 좋다고 합니다. 
+다 먹으면 재구매 할겁니다!!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>26.04.12.</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>aved*****</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>고등학생인 아들이 에너지드링크를 마시는데 매번 마음에 걸리더라구요 
+중간고사 기간이라 고민하고 있었는데 
+미미미누님이 광고 보고 바로 주문했어요 
+아들이 효과가 있다고 하네요 샤인머스캣이 맛있다고합니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>26.04.15.</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>cron*****</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>피로하고 잠이 부족해서 수업시간 그 외에도 졸음때문에 문제가 많았는데 효과 넘 좋아요.
+오렌지맛은 오렌지맛은 없고 먹기는 편해요.
+샤인머스킷은 맛과 향은 좋은데 뒷맛에 쓴맛이 좀 나요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>26.04.12.</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>la****</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>시험기간이라 아이가 사달라고 하더라구요. 친구가 하나 줬었는데 효과가 있더라고.
+되도록 커피는 마시지 않게 하고싶어서 사줬어요.
+아이는 잘 맞다고 하더라구요. 
+리뷰상 오렌지가 더 맛나대서 이 구성으로 사줬는데 아이가 아직 샤인머스켓 맛은 안봐서 리뷰는 어렵네요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>26.04.21.</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>jung*****</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>중간고사  앞둔 아들땜에  주문했어요
+에너지드링크  커피를 먹는것땜에 걱정됐는데
+이걸 우연히 알게되서 구매했네요</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>26.04.17.</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>cool*****</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>고등학생 딸아이가  너무 졸려워해서 구매했습니다.
+먹자마자 바로효과가 나서 무리없이 새벽2시까지 공부할수있었다고 합니다. 아침에 2포 챙겨가더라구요~^^</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>26.04.19.</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>toma******</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>중간고사 얼마남지 않아서 구매해봤어요
+아직1.2회 먹어서 효과가 있는것 같기도하고?아직 잘 모르겠다고 하네요..
+좀 더 먹어봐야겠어요 ㅎ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>26.04.14.</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ksqk******</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>중고딩 딸들 중간고사 기간에 카페인 음료 마시는것보다 좋을것같아 인스타 광고보고 반신반의하며 사봤는데 애들이 오랜지맛은 별로긴한데 효과는 있다고 합니다 다먹고 또 구매해야겠네요</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>26.04.18.</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>jenn****</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>지난번에도  한번  구입해  먹어보구  재고매  원해서  또  구매해요  아이가  좋아하네요</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>26.04.16.</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>pj****</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>샤인머스켓 맛은 넘 쓴 맛이 있어서 오렌지 맛으로 사봤어요. 효과는 잘 모르겠지맠 에너지 드링크 먹는 것보다 나을꺼 같아 재구매 합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>26.04.09.</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>jand*****</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>에너시슬은 젤리 형태라서 학교에 가지고 다니면서 먹을 수 있어서 편리합니다. 맛도 좋다네요.  잠이 좀 깬다고 해서 효과는 괜찮은 것 같습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>26.04.21.</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>whdf*****</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>그렇게 챙겨주던 영양제는  먹지도 않는 아들~
+사서 이 역시 안 막을까 걱정했더니 말 안해도 하나씩 잘 챙겨 먹네요 ㅎ</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>26.03.12.</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>kjs2****</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>커피는 개인적으론 맛도 없고 
+치아착색 때문에 먹기 싫어서 
+열심히 검색하다가 이거 샀어요
+홍삼스틱이랑 비슷한 크기라 학교가기 전에 
+후다닥 챙겨서 걸어가면서 먹기도 좋아요!
+어제 밤에 오자마자 맛궁금해서 하나 먹고
+잠 잘 못 자고 쌩쌩했던거 보면 
+효과도 분명해요 (낮에 꼭 드세요)
+다만 리뷰에선 샤인머스캣맛 맛있다고 하던데
+저한텐 그냥 요즘에 새로나온 아임비타 음료에 약간의 샤인머스캣향이 첨가된듯한
+건강해지는 맛이었어요.....
+그래도 너무 만족해요 나중에 떨어지면 
+또 사러올게요</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>26.04.19.</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ivor****</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>아이먹이려고 샀는데 맛있다고 하네요
+먹고2시간후 반응이 오는거 같다면서
+앞으로도 계속먹을듯해요</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>26.04.21.</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>doui***</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>중3 아이가 피로해보여 먹이게 되었습니다. 맛있는지 잘 먹고, 밤에 좀 덜 피곤해보이는 것 같기도 하네요</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>26.04.21.</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>sh****</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>고3딸아이가 친구들이 많이 먹는다고 사달라고해서 구매했어요. 피곤함이 나아지길 바래요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>26.04.13.</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>defi****</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>고3   고2인 우리 딸들이  효과있대서 두번째 구매입니다~한 포 가격이 저렴한 아메리카노 한 잔 값이네요ㅎ부디 이거 먹고 컨디션 좋아져서 노력한 만큼 값진 결과 얻길~^^</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>26.04.19.</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>qod3*****</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>아이들 공부하다가 정신환기할때 한개씩 먹어보라고 주문했어요
+ 젤리라 맛있고..  거부감없어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>26.04.16.</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>suns******</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>주위 친구들 다 먹는다고 해서 사줬어요
+오자마자 한개 바로 먹었어요
+중간고사 준비기간 잘 활용해 보려고 합니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>26.04.16.</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>j2y2***</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>수험생 필수품 이네요 맛도 두가지라 골라먹는 재미가 있네요 ㅎㅎ 집중력 팍팍 충전 되는 느낌이고 맛도 있네요^^</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>26.04.22.</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>isul***</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>필요할때마다 먹으려고 샀습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>26.04.12.</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>cray*****</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>공부하는데 조금이라도 도움이 되었으면 하는 마음으로 주문했는데 먹는것도 편하고 도움이 된다고 하네요~^^ 맛은 샤인맛이 먹기 더 좋다고 하네요~</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>26.04.16.</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ge****</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>중고딩 아이들 시험기간이라서
+영양도 챙기고 카페인 도움도 받아서
+좋습니다.  단 가격만  쬠 싸면 좋겠어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>26.04.20.</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>only*******</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>몸에 조금이나마 해를 덜 주기위해 구입했어요. 효과가 있기를요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>26.04.19.</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>5재구매</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>sala******</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>아이들 위해서 늘 쟁여놓는 만족템입니다. n번째 재구매중!</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>26.04.17.</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ch****</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>중간고사 준비중인 딸 커피는 절대 싫어해서 집중샷으로 열심히 먹고있어요. 화이팅!!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>26.04.12.</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>sa****</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>소문듣고 구입했습니다 고등학교 2학년 딸아이에게 잘 맞았으면 좋겠습니다. 효과가 있었으면 좋겠네요</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>26.04.14.</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>suny*****</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>시험기간이라 더 자주 구입하게 되네요.
+맛도 좋아서 고등학생 아이가 좋아합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>26.04.14.</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>cris****</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>수험생아들이 피곤해해서 주문해봤어요~
+안졸립다고하네요~^^
+좀더 먹여보고 효과있으면 재구매 하려고합니다~</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>26.04.04.</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>skyh******</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>아이 시험기간 대비로 샀어요
+평소 젤리를좋아하는 아이라. 거부감없이 잘 먹었답니다.
+샤인머스켓맛이 좀 더 맛있다고하네요.
+너무달지않았고 졸음도 덜 오는것같다고하네요~</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>26.04.21.</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>pris****</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>고딩 중간고사 기간에 필요하다고해서 사줬는데 잠도 덜오고 맛도 좋다 하네요</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>26.04.16.</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ojuo*****</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>배송도 빠르고 유통기한도 넉넉해요
+할인해서 저렴하게 잘 샀어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>26.04.13.</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>arin***</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>고2아들이 에너지 음료 자주 마셔서 구매했어요
+식물성이라고 해서 몸에 좋겠죠
+먹어보고 후기 더 작성할께요</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>26.04.15.</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ljsc*****</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>아이 곳인데  몬스터 마시는것보다 나을것 같아  구매했어요.  아이도  시험때 먹기 좋다고 하네요</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>26.04.15.</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>risi*******</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>늘 먹고 있는제품입니다^^
+덜피곤 하다고 아이가 이야길 해서 만족하고 있습니다~~</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>26.04.14.</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>tmdr*****</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>고등학생 아들을 위해 주문했어요~
+시험기간에 도움이 됐으면 좋겠네요~^^;</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>26.04.22.</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>pjs1***</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>안먹은것 보다 집중이 잘되는거 같아요</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>26.04.19.</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>zwls***</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>아이가
+잘 먹네요
+추천합니다
+배송빨라요</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>26.04.14.</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>5재구매</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>deat*****</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>고2애들이 다른약은 손에 쥐어줘야 먹는데 이건 군말안하고 챙겨먹네요 ㅎㅎ 편해요</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>26.04.11.</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>dubu****</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>시험기간이 다가와 피곤해하는 아들에게 먹이고 있습니다.  먹기도 편하고 맛있어서 꾸준히 잘 먹네요~</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>26.04.15.</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>dcji*****</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>오렌지맛이 입맛에 더 좋다고 하네요~재구매입니다~영양제이니 좋겠지요^^</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>26.04.15.</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ksh7*****</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>식물성 카페인이라고 해서 에너지 음료 먹는것 보다는 나을것 같아서 먹여 보려고 합니다 효과 좋으면 좋겠어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>26.04.21.</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>mida****</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>고등학생이 먹고있습니다 계속 주문해서 먹는중입니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>26.04.08.</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>suns***</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>고3 아이를 위해 구입했어요
+드라마틱하게는 효과가 없지만
+ 안먹을때보다는 집중이 되는것같고 덜졸린거 같다고하네요 ㅎ</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>26.04.19.</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>lms7***</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>배송도 빠르고 아이가 집중력에 도움이 된다네요...</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>26.04.22.</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>bccb*****</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>잘 받았습니다.
+감사합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>26.04.18.</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>72****</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>도움이 됩니다. 2번째 구매입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>26.04.07.</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>meti****</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>아이 고등학교 올라가고 첫 시험기간이라 먹여보고 있어요. 아직은 잘 모르겠지먼 도움될거라 믿어요!</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>26.04.20.</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>swee*******</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>아이는 오렌지맛보다 샤인머스캣맛이 더 맛있다고 하네요</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>26.03.30.</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>free********</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>두번째 구매구요. 이번에 할인해서 다시 샀어요. 조금 싼 다른 제품 먹다가 이거 사주니까 아이들이 대웅 에너지씨슬이 더 맛있다고 하네요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>26.03.29.</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>he****</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>학교학원 과제때문에
+잠은 부족하고 공부양이많아
+피곤해해서 구매해줬는데
+첫째는 잘모르겠다고 하고 둘째는
+효과있다해서
+시험기간 일주일전부터
+늘 구매해서 먹이고있어요
+새로나온 샤인머스캣맛이
+아이는 더 맛나다고하네요~~</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>26.04.18.</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2zhy***</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>덜 피손한 것 같다고 해서 고등학생 아이 시험기간에 먹고 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>26.04.19.</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>cute*****</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>애가 잘먹어요 효과있길</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>26.03.28.</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>elro***</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>아이 공부할때 체력건강 키워주고싶어 구매했는데 아이도 이제품을 먼저알고있더군요 아이들사이에 인기가있는가봅니다. 잘먹고 공부체력에 한껏도움이 되었음하는 아빠맘입니다 ,   ㅎㅎ</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>26.03.29.</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>tuga******</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>배송이 너무 빨라서 구매 후 바로 섭취할 수 있고 알약 형태로 되어 있는 에너씨슬을 복용하다가 조금 더 효과가 있을 것 같아서 재구매 했는데 만족스럽네요^^</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>26.04.07.</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>9934***</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>고등학생 아들 위해 항상 잘 구입하고 있어요~^^
+더 많은 혜택 재구매쿠폰 같은게 있으면 더 좋을꺼 같아요~^^</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>26.04.01.</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>heam******</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>고등학생 딸이 먹습니다
+아무래도 커피나 고카페인 음료보단 나을것같아서요 시험기간때는 친구들도 나눔해서 같이 먹네요
+효과는 확실히 있는것같아요
+다만 다음날. 피곤하다는거 빼고는요~~~</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>26.04.18.</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>sosi*****</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>요즘 수험생들에게 관심이 많다고 하는데
+약효 기대됩니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>26.04.18.</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>shin********</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>피로 회복용으로 간편하게 먹기 좋아요</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>26.04.20.</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ms****</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>애가좋아하니좋은가보다합니다 고3입니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>26.03.31.</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>yun2***</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>고등학생 아들 학교에서 졸립고 피곤해 해서 사봤는데 오늘 처음 먹고 갔는데 효과가 있었으면 좋겠습니다. 오랜지맛은 조금 시큼하다고 하네요. 먹기 부담스러울 정도는 아니에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>26.04.21.</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>amor*****</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>시험때마다주문.샤인머스캣맛잇대요</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>26.04.18.</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>4한달사용</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>u1****</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>약간 쓴맛이 있는데
+샤인머스캣 맛은 괜찮다고 하네요</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>26.04.16.</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>grow******</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>아이가 잘먹고 효과있다고 해서 계속 구매중입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>26.04.11.</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>augu*****</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>피곤할때 먹으려고 구매했어요. 젤리 타입이라 먹기 편할것 같아요</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>26.04.15.</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>5재구매</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>bomu***</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>아이 말로는
+맛이 있진 않은데 먹으니 잠은 안오는 거 같다고 합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>26.04.15.</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>5재구매</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>bomu***</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>아이 말로는
+맛이 있진 않은데 먹으니 잠은 안오는 거 같다고 합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>26.04.19.</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>garu******</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>수험생 효과 좋다고 해서 주문했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>26.04.04.</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>r9****</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>아이가 친구가 준 걸 먹고 졸립지 않다고 구매해 봤습니다. 가격이 비싸지만 기존 카페인 음료보다 부담이 덜하길 바라봅니다~</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>26.04.09.</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>owne***</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>부담없이 먹기 좋아요 효과는 더 먹어 봐야 할듯해요</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>26.04.19.</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>pa****</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>중3 효과 있다고해서 추가구입했어요~</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>26.04.17.</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>yu****</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>고1 아들이 에너지 드링크를 찾기 시작하자마자 샀습니다. 맛있게 부담없이 먹을 수 있어서 좋아요 중간고사 앞두고 있는데 도움이 되었습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>26.04.18.</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>sk****</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>아이 시험기간에 좋아요</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>26.04.07.</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>hy****</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>아이들이 공부하면서 졸릴때 잘 먹고 있어요
+알약이 아닌 젤리라 먹기 편해서 좋아요</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>26.04.02.</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>tell****</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>고등학생 딸이 먹고 있어요
+샤인머스켓 맛으로 먹어보고
+이번엔 오렌지 두통 같이 사봅니다
+잘 먹고 도움되길…</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>26.04.18.</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>yong*****</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>먹고나면 확실히 피로가 덜해보여요</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>26.04.19.</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>love***</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>항상 구매하고 있어요
+추천합니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>26.04.04.</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>hj****</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>커피 대신에 먹기 좋습니다. 먹고 나면 확실히 효과가 좋아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>26.04.13.</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>alca***</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>효과는 꾸준히 먹어봐야 알겠지만 일단 맛은 괜찮다고 합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>26.04.07.</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>qlso***</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>중건고사 앞둔딸을 위해 구매했어요.알약 먹기 싫어하는데 이건 잘 먹어요!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>26.04.14.</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>jini****</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>아이가아침저녁하나씩 먹고있는데
+효과는조금더봐야할거같아오ㅡ^^</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>26.04.06.</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>kidj***</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>아이가 효과가 좋다고 하네요- 남편도 하나씩 챙겨 먹는 중이라 추가 구매할듯해요</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>26.04.13.</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>tomi****</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>너무 좋아서 계속 주문해서 먹고있어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>26.04.19.</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>sala******</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>수험생위해서 n번째 재구매중!</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>26.04.15.</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>ha****</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>고3  중간고사기간이라 먹고 잘 해내고있어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>26.04.15.</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>suss*****</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>아이들에게 나눠주기 좋아요</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>26.03.22.</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>tokk******</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>배송도빠르고좋아요
+포장상태도꼼꼼하게잘받았습니다
+맛있어요 만족합니다
+재구매하고싶네요</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>26.04.08.</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2004***</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>고등학교 1학년 중간고사 응원하려고 구매했는데 먹기 편하고 피곤한게 덜 하다고 하네요</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>26.04.21.</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>imok****</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>고1 남자아이 중간고사 앞두고 사달래서 사줬는데 괜찮은거 같다고 하더라구요. 효과있었음좋겠어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>26.04.02.</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>donc***</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>고등학생 아들 위해 샀어요.
+가격은 좀 비싸지만 핫식스나 몬스터보다 건강에 좋을 거 같아 구매합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>26.04.11.</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>bi****</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>일단 먹기 편하고 효과가 생각보다 좋아요</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>26.04.09.</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>kyy7***</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>배송이 빠르고 배송상태도 좋아요</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>26.04.01.</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>love****</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>고3 아들이 친구한테 받아서 먹어보고 주문 해 달라고 해서 주문했습니다.꾸준히 먹어 보려고 합니다.힘내라~우리 고3들~!!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>26.03.30.</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>kito****</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>우연히 접한 상품인데 카페인이 필요할 때 간편하게 그리고 건강하게 먹을 수 있을듯 해 구매했어요. 효과 있었음 좋겠네요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>26.04.04.</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>moth******</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>고3맘입니다
+이제 중간고사를 앞두고 아이가 믿고 잘 먹고 있어요
+아주 만족하며 먹고 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>26.04.06.</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>jayu***</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>카페인 음료를 마시면 화장실을 자주가야해서 젤리로 먹고있어요
+맛도 좋네요</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>26.04.17.</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>k0****</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>잘받았습니다 
+잘 먹을게요</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>26.04.16.</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>ilov*****</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>등교길에 하나씩 꼭 챙겨갑니다~!</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>26.04.20.</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>pigl******</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>시험기간이라 또 구매했네요 ㅠ 샤인머스켓 처음 구매했는데 만족도 아주 높네요~</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>26.03.27.</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>tc****</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>고3 아들이 만족하면서 꾸준히 복용중입니다. 드라마틱한 효과는 없지만 그래도 안먹는날하고 차이가 있나봐요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>26.04.22.</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>dalk***</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>고3 수험생 꾸준히 먹고 있어요..집중력도 높여주고 체력까지 챙기니 좋아요</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>26.03.31.</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>jbey****</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>늘애용합니다 대웅제약 라이브때 구매 쿠폰이용해서 더 좋았어요 잘 활용합니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>26.04.10.</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>ice1***</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>아이 시험기간이라 구입해봅니다
+효과있었으면 좋겠어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>26.04.09.</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>deep***</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>시험공부하는 딸램 주려고 샀는데 효과있다해서 바로 재구매했어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>26.03.29.</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>jjin****</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>수험생 딸아이 필수템입니다. 이번 모의고사때 사놓은게 없어 당황했어여. 필수템!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>26.04.15.</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>zzon*******</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>개인차가 있겠지만, 에너지드링크에 비해서는 잠이 잘 온다는 따님이십니다^^ 하지만 여러모로 에너씨슬이 낫기에 먹여볼려고 합니다. 그리고 다른 젤리스틱에 비해서는 맛있다고 합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>26.04.08.</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>wlal****</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>고3  아들에게 주려고 샀습니다. 먹어보고 또 구매할께요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>26.03.27.</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>yrch*****</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>딸아이 중간고사 앞두고 구매해 보았어요.
+한번 먹어보고 덜 졸렸다고 하긴하는데... 효과는 좀더  지켜봐야겠죠?ㅎㅎ</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>26.04.08.</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>cuty****</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>아이가 공부하면서 잘 챙겨먹어서 아직 남았지만 재주문했어요~</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>26.03.31.</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>morg****</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>고딩 딸아이한테 주기 딱인거같아요. 아이가 좋아하네요. 꾸준히 먹여볼게요</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>26.04.12.</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>shin*****</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>고딩이 시험기간이라 구입해봤어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>26.04.12.</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>elin*****</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>효과 좋습니다.
+먹기도 편해요^^</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>26.04.13.</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>best***</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>집중이 필요할 때 효과적입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>26.04.05.</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>bh****</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>아이 시험기간이면 준비하는데 이름있는 회사제품이라 신뢰가 가서 꾸준히 사요'</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>26.04.05.</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>brad***</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>고등학생 딸 사줬습니다. 효과가 좋으면 좋겠네요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>26.04.06.</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>kata******</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>포장도 꼼꼼하고 배송도 빠르고 제품 좋아요 😀 맛있어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>26.04.09.</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>jjon****</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>먹기 편하고 힘이 나는 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>26.04.13.</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>ym****</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>먹기부담없고 간편해요</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>26.03.28.</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>fose*****</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>커피대신 피로회복과 집중력 향상을 위해 구매했습니다. 추천받아 구입했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>26.04.09.</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>wend*****</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>시험기간 필수템 재재구매중</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>26.03.22.</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>frag******</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>아이가 아침 등교전 꾸준히 먹고 있어서 주문했어요. 아침에 입맛 없어서 다른건 잘 안먹는데 그나마 이건 먹기 편하다고 해서 먹고 가요. 효능까지는 그닥 모르겠긴 하네요ㅎㅎ</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>26.04.07.</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>yun6***</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>커피를 못마시는 아들이 잘 챙겨 먹어서 좋습니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>26.04.07.</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>dygk*****</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>고등 딸아이가 먹는거예요
+먹으면.안졸리고 좋다네요 😊</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>26.04.03.</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>crom****</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>힘들때 먹었더니 좋아요. 
+온 가족이 먹어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>26.03.31.</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>ko****</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>집중할때 좋다고 해서 재구매했어요. 가격만 좀 저렴하면 좋겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>26.04.08.</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>cara******</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>고등아이가 사달라고해서 주문했어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>26.04.21.</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>love******</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>선물용으로ㅈ구매했는데 포장도 꼼꼼하고 받는 사람도 매우 만족해 했어요~^^</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>26.04.11.</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>choc*****</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>고3 아이가 요청해서 구매해 주었는데, 졸리움 등에 효과가 있다 합니다
+다만, 부모 입장에서 보조적 수단에 의해 조절하기 보다는 자신의 의지로 조절했으면 하는데ᆢ
+현 시점에서는 심리적 불안 등으로 쉬운게 아니어서 구매해 줘봤네요</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>26.04.11.</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>chin****</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>좋은 제품 잘 사용할께요~~</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>26.04.08.</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>rhyt****</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>피곤해하는 수험생을 위한 영양제~</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>26.04.14.</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>vert****</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>수험생 아이에게 사주었는데 확실히 잠덜오고 집중도도 높아진다고 하네요 시험기간마다 사먹일려고 합니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>26.04.06.</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>acce***</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>떨어지지 않게 구매해서 쟁여놓고 있어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>26.04.20.</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>bcmi***</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>수험생 아들이 먹기 좋고 아주 만족한다고해서 재구매 했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>26.04.06.</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>ju****</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>고등학생 아들 챙겨주려고 샀는데 잘 먹네요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>26.04.21.</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>bonb****</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>카페인 음료 먹는 딸 때문에 구입했는데 만족스럽데요~</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>26.04.09.</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>susa******</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>배송빠르고 포장꼼꼼해요.
+아이가 좋아하네요.
+감사합니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>26.04.06.</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>ta****</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>빠르게 잘받았습니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>26.03.28.</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>jazz******</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>고1. 하루3포 먹으며 닥공하고있어요. 졸업때까지 꾸준히 먹이려구요</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>26.04.03.</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>sj****</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>시험 전이라 사봤는데 효과좋으면 또 사러 올게요~</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>26.03.20.</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>hani****</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>제딸래미는 오렌지가 맛있다던데 제조일자보니 샤인머스캣이 더 잘나가나봐요. 오렌지는 몇달전에 시킨거랑 동일하네요</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>26.03.04.</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>1771******</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>카페인 마시면 속쓰림이 있어 커피도 안마시는 아이인데 집중샷은 시험기간에 꼭 챙겨 먹습니다. 특히 시험 준비나 시험 당일에는 본인이 꼭 챙깁니다. 비타민은 안챙겨먹는데 이건 스스로 챙겨 먹으니 효과가 있는거 같습니다.
+행사할때 미리 쟁여놓습니다!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>26.04.01.</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>nssa******</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>가지고다니기  편하고  먹기편해  좋아요</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>26.03.10.</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>jand*****</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>다른 젤리 제품들보다 맛이 더 좋다고 해서
+요걸로 재구매했습니다.  
+아이들 공부할 때 커피나 에너지음료보다는 
+건강 관리하기에 도움이 되고 있습니다.
+ 야간자율학습시 섭취하기 위해 학교에 
+가지고 다니기에도 좋습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>26.03.24.</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>5재구매</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>cher******</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>고딩아이 집중해서 공부하도록  꾸준히 챙겨주고 있어요. 피곤함이 덜한거 같아요</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>26.04.12.</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>p980****</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>잘 먹겠습니다 ~~~~~</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>26.04.07.</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>lsy0***</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>샤인머스ㅅ 맛이 훨씬 맛있어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>26.04.04.</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>chgm*****</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>아들 시험 공부를 위해 주문했어요~~</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>26.03.22.</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>0616***</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>시험 앞두고 지인 추천으로 구매했어요.
+먹고 효과보면 재구매 해야죠~</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>26.04.11.</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>sung*****</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>고딩이라 늘 잠이 부족하니
+카페인음료 마시곤 해서 걱정이 되어서
+지인추천으로 구입했는데 먹어보고  좋다고 하네요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>26.03.27.</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>jmpa****</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>수험생 아이들을 위해 구입했는데 효과 있다고 해서 커피 대용으로 재구매했어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>26.04.05.</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>ooga****</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>아이가 맛있게 먹습니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>26.03.27.</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>ly****</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>아이들이 계속 찾아서 또 주문합니다
+추후 또 주문할게요~</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>26.03.31.</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>dola*****</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>고3아들이 먹고난 후 확실히 덜 피곤하다고 하네요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>26.04.05.</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>k_****</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>딸아이 선물로 사줬어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>26.04.14.</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>fo****</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>애들 주려고 샀다가 저도 먹어요
+회의나 중요 미팅때 집중 빡~! 좋네요</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>26.04.01.</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>sek9***</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>고등학생 아들  먹으니 덜 피곤하다고 하네요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>26.03.22.</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>hyue*****</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>겨울에산 제품과 오렌지맛은 유통기한이 똑같네요 그래서 별 뺐습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>26.04.19.</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>99sf***</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>아주좋아요 좋아요 좋아요</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>26.04.12.</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>so****</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>시험기간 필수템이에요. 아이는 둘 다 맛있다고 하네요^^</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>26.03.19.</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>ku****</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>딸아이가 고등학생이 되면서
+학교생활에 야자에 학원에
+피곤해해서 야자에 피곤하면
+먹으라고 구매했습니다
+확실히 먹고 나면 잠도 깨는 것 
+같다고 가방에 챙겨가네요~~</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>26.04.02.</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>rick****</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>배송도 빠르고 맛도 괜찮습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>26.04.02.</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>ilso****</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>아이들이  부담없이 잘 먹습니다'</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>26.03.21.</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>or****</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>생활 활력이 쑥쑥 올라 가네요
+또 구매하려고 합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>26.04.13.</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>hari****</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>아들이 잘먹어요. 다먹으면 또 주문할께요</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>26.04.13.</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>marj*****</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>효과가 있는지 잘 모르겠어요. 아이가 먹고도 잠온다고 하는데</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>26.03.17.</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>ch****</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>고등학생 아이가 꾸준히 먹는중이에요~ 이번에는 샤인머스캣맛도 같이 주문해봤는데 맛있다고합니다~^^</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>26.03.25.</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>hush******</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>아이에게 조금이라도 도움이 될까하여 구매합니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>26.03.15.</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>grow******</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>고딩 아이에게 주려고 구매했습니다.
+아이가 효과좋다고 만족스러워 합니다.
+재구매 의사 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>26.03.28.</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>yunk****</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>기획으로 싸게사서 좋아요</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>26.03.21.</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>swee*******</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>빠르게 잘 받았습니다 지인 추천으로 구입했어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>26.03.23.</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>nayu****</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>오렌지맛 먹다가 샤인머스캣이 나왔다고 
+시켰는데 아이가 오렌지보다 샤인머스캣이 더 맛있다고 하네요</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>26.03.31.</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>susu****</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>공부할때 도움이 돼요</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>26.03.22.</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>brel*****</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>맛있다고 하네요 젤리보다 액상이 오렌지쥬스같대요</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>26.03.27.</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>5재구매한달사용</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>flow*******</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>고3 아이에겐 이젠 필수일정도로 잘챙겨먹네요..</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>26.03.26.</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>ssii*****</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>간편해서  들고다니며  먹기좋아요</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>26.04.18.</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>magm****</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>항상 쟁여두고 먹는거라 주문</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>26.03.14.</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>u1****</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>리뷰가 너무 좋아서 주문했어요
+아이들이 효과 있었으면 좋겠어요
+먹어보고 다시 리뷰 쓸게요~</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>26.03.21.</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>only***</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>졸음 방지에 효과가 있는 것 같고 오렌지 맛 보다는 샤인머스캣 맛이 먹기 수월합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>26.03.19.</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>oliv********</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>맛의 느낌은 샤인머스캣이라 오렌지랑비슷하지만 아이는 샤인이 더 좋다네요^^</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>26.04.21.</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>woor*****</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>잘 받았습니다~~^^</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>26.03.20.</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>ho****</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>아이가 먹고. 효과 좋다고 해서 재구매 합니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>26.04.12.</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>4한달사용</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>ome0***</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>효과는 어쩐지 몰겠으나 딸아이가 습과적으로 먹는듯</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>26.03.04.</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>han1****</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>먹고나서 조금지나면 피로가 해소되는 느낌을 받을수있어요. 맛도 오렌지 샤인머스캣 두가지맛인데 약간 신맛이 있지만 맛있게 먹을수있어요. 개인적으로 샤인머스캣맛이 더 좋네요~*^</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>26.03.28.</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>kski*****</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>수험생에게 선물했어요^^</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>26.03.23.</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>leec*****</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>먹기편하고애들이 좋아해요</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>26.04.14.</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>nals***</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>애들 셤 기간이 다가와서 구매해요</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>26.03.26.</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>br****</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>상자가 다부서져서왔어요 찝찝하네요</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>26.03.27.</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>shar***</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>계속 재구매중이에요</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>26.03.15.</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>lms7***</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>배송도  당일배송이라 빠르게 잘보내 주셨고  아이가 학원다니면서 먹기 편할꺼 같아요...</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>26.03.18.</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>shj8***</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>아이가 맛있고 효과도 있는것 같다고 만족했어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>26.04.05.</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>eunj********</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>맛은 괜찮다네요.
+괜찮은거 같아요</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>26.04.10.</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>them*****</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>수험생 피곤할때 복용합니다
+몸에 잘 맞아 재구매합니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>26.03.23.</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>jsmm***</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>먹기  편하고 상품 좋아요</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>26.04.10.</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>noa0*****</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>좋아요 좋아요 좋아요</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>26.03.04.</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>maso******</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>아이들 집중력 떨어지거나 졸릴 때 효과가 좋다고 해요. 아이들이 먼저 찾아요. 두가지맛 번갈아가며 먹는데 샤인머스캣을 더 좋아하긴 해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>26.03.27.</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>razh******</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>배송이 빨라요...</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>26.04.11.</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>logi*****</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>가격, 배송, 제품 모두 만족합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>26.03.10.</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>yuri******</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>새로 나온 샤인머스켓맛 너무 맛있다네요. ㅅᆢ험생 아들 에너지 음료 대신 이거 먹으라고 사줬더니 도움 된답니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>26.03.11.</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>sook****</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>꼬박꼬박 아이가 질 챙겨 먹어요.샤인머스키는 또 구입했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>26.04.14.</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>5재구매</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>kang***</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>피곤 할때 챙겨 먹고 있어요~</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>26.03.17.</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>ippi****</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>아들이 공부할 때 잘 먹고 있습니다 집중이 잘 된다하네요</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>26.04.10.</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>j0****</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>집중력이 좋아졌어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>26.04.09.</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>cem1***</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>아이가 잠도 잘깨고 집중력도 좋아진다고 해요</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>26.04.08.</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>shar*******</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>진짜 피곤이 줄고 집중이 되서 좋아요</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>26.03.18.</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>jeey******</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>수험생아이에게 도움되길 바래요</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>26.03.17.</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>5재구매한달사용</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>we****</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>고등학생 아이가 졸릴 때 먹는다고 알아서 챙겨가네요</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>26.03.19.</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>bg****</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>학교에서 졸릴때 먹어보려구 주문합니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>26.04.04.</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>lv****</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>먹기 편리하고 집중하는데 도움이 되는 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>26.03.15.</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>sala******</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>수험생 주려고 샀어요 효과있길 바래요</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>26.03.19.</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>soil****</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>먹으니 피곤함도 들하고 먹기편해요</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>26.02.22.</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>hbhr****</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>첫째는 오렌지, 둘째는 샤인머스켓 좋아해요.
+졸릴때 먹으면 정말 잠이 깨고 도움이
+된다고 해서 재구매합니다.
+유통기한 아주 넉넉하구요
+한 달이면 다 먹을것 같아요</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>26.03.13.</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>tomi****</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>아이가 공부하는데 피곤해해서 먹이고 있어요
+너무좋아요</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>26.03.16.</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>koli***</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>아이 시험 공부용으로 미리 준비 효과 있어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>26.03.19.</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>4eve****</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>딸아이가 사달라고해서요</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>26.04.07.</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>kbr1****</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>저희 아이는 효과가 좋다고 하네요</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>26.03.14.</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>best***</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>맛에 거부감이 없고 40대도 하루 2~3포 정도 먹으면 효과가 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>26.03.08.</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>flut*****</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>전에 타사 다른제품은 
+아이가 속울렁거림같은게 있었는데 
+이제품은 잘먹고 있어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>26.04.03.</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>sone*******</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>아이가 먹는다샀는데 좋다고해서 재구매예정이에요</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>26.03.09.</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>soul***</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>저희애들 요고는 꼭 챙겨먹을정도로 항상 주문하는 제품입니닷^^</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>26.03.27.</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>crys*****</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>수험생 집중력관리 필요해서 구입했어요.
+가격이 좀 내렸으면 좋겠어요 ㅎㅎ</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>26.04.04.</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>iy****</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>간편하게 먹게되어있어요
+효과도 좋으면</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>26.03.19.</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>1789******</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>저희딸이 학교에서 친구한테서 먹어봤는데 효과가 좋은거 같다고하더라고요. ..종종 이용하겠습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>26.04.06.</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>au****</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>효과가 있길 기대합니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>26.04.05.</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>myj4***</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>맛도 무난하고 먹기 편리합다</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>26.03.04.</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>ko****</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>타우린 들어있어서 피곤이 풀리는 느낌이네요.
+박카스 찐한 맛 같애요</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>26.03.31.</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>mrop***</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>배송도 빠르고 먹기도 좋아요</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>26.03.07.</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>fa****</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>아이가 피곤할때 먹는데 효과가 좋아요
+잠이 안온다고 하네요</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>26.03.04.</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>gudr****</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>수험생 상비템입니다~
+먹기 편하고 상큼하니 잠이 깨고 효과가 좋다네요</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>26.03.15.</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>72****</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>낱개 포장으로 편리해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>26.04.06.</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>leej*****</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>정말 효과 있는 듯요!!!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>26.03.26.</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>tomo****</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>아들이 먹어보고 괜찮다고 해서 또 구매했어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>26.03.09.</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>jrki***</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>수험행 딸아이 세번째 주문입니다
+오렌지 샤인 둘다 맛있어요~
+먹고나면 힘도 나고 잠도 깨고 
+심리적인건지 모르겠지만 컨디션 회복에 훨씬 좋다고 하네요</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>26.03.09.</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>we****</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>효과 있는듯 하여 재구매해 먹고 있어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>26.03.12.</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>woow***</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>고딩아이가 잘 먹어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>26.02.13.</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>yuri******</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>고3  아들 위해 샀어요. 에너지 음료 대신 먹으니 좋대요. 샤인머스켓 맛은 처음 주문했는데 웬만한 젤리보다 맛나다네요. 맛도 좋고 잠도 깨고 건강에도 좋으니 일석삼조네요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>26.03.27.</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>mati*******</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>빠른배송 감사합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>26.03.23.</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>king******</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>수험생 아들이 피곤하다고 해서 사줬는데 먹기 간편하고 좋다고 계속 사달라고 해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>26.03.07.</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>99sf***</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>아주편하고 맛도 좋아요</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>26.03.15.</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>rtn0***</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>수험생 아들이 잘 먹고 있어요  가격이 좀 비싼거 빼곤 좋아요</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>26.03.24.</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>yj****</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>배송이 빠르고 좋아요</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>26.02.23.</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>bo****</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>맛있고 잠 깨는데 좋은 것 같아요. 다만 너무 늦은 시간에 먹으면 잠이 안 올 수가 있어요~</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>26.03.26.</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>them*****</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>고등학생아이 학원 가기전에 먹어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>26.02.19.</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>4한달사용</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>ultr**********</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>아이가  졸릴때 하루 한두포 먹고 있습니다  아이가  효과 있다고 사달라해서
+작년부터 떨어지면 계속 사고 있는데
+ 계속 꾸준히 먹어도 되는지 걱정이
+되기도 합니다 맛은 둘다 괜찮다고 합니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>26.03.20.</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>cool****</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>배송빠르고 효과도 좋아요</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>26.03.06.</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>suns***</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>고3딸을 위해 구입했어요~</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>26.02.14.</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>lees********</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>2가지 버젼으로 구매했어요
+아이가 잘먹고 있다해요</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>26.03.25.</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>99****</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>오렌지가 더 강력한듯</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>26.02.24.</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>gugu****</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>아직 먹어보진 않았지만 3월에 아이에게먹여보려고 미리 샀습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>26.03.20.</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>ta****</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>고등학생 자녀들이 사달라고 하네요</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>26.03.19.</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>zeni********</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>맛있고 확실히 집중과 몰입이 잘됩니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>26.03.12.</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>dash***</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>맛은 박카스랑 이것저것 섞인 맛있었는데 확실히 먹고나니까 집중력이 확 올라갔어요^^</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>26.02.25.</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>lv****</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>먹으면 덜 피곤하고 잠이 깹니다. 맛있어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>26.02.22.</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>prsu*****</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>빠른배송 아주 좋아요</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>26.03.14.</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>es****</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>맛도 괜찮고 먹기편하고 잠이 깨네요</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>26.02.21.</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>jsmm***</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>배송빠르고 상품 좋아요</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>26.03.13.</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>ome0***</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>고등딸이 학교에서 반나절은 졸린다해서 구입했어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>26.02.17.</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>cher******</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>집중력에도 좋고 면역력에도 도움되는것같아 늘 챙겨주고 있어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>26.02.21.</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>lsy0***</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>빠른배송감사합니다 ^^</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>26.02.19.</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>99****</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>맛은 샤인머스켓이 더 나은데 잠깨는건 오렌지맛이래요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>26.02.07.</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>imje***</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>공부하다 잠깰때 도움된다고 좋아하네요. 샤인머스켓 맛과 함께 있어 더 좋은 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>26.03.03.</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>nath****</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>아들이 이건 꼭 챙겨먹어요. 카페인 음료 줄일 수 있어서 좋아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>26.02.21.</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>pjs1***</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>공시생인데 먹고 이득 보길 바랍니다 ㅎㅎ</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>26.02.13.</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>comp****</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>고등학생 딸 공부 하면서 잠 오면 카페인 음료를 마셨는데 이거 먹고 잠 안 온다고 해요</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>26.02.06.</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>kang***</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>아이들과 함께 먹으려고 주문했어요. 
+좋다고 하길래 꾸준히 한번 먹어보려 합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>26.02.17.</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>hs****</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>샤인맛머스켓 괜찮네요</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>26.03.03.</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>jjin***</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>먹기시작한지 오래되진 않았지만 좋은거 같아요</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>26.02.15.</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>leec*****</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>애들이 맛있다고 잘먹네요 좋습니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>26.02.18.</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>5재구매</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>flow*******</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>고3아이가 늘챙겨먹네요</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>26.02.12.</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>is****</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>먹으면 확실히 정신이 맑아지고 집중이 잘된다고 합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>26.02.14.</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>5재구매</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>we****</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>집중력에 효과 있어 재구매했어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>26.03.06.</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>go****</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>매우 잘먹고있습니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>26.02.07.</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>ok****</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>시험전후에 먹어보더니 이젠 피곤하면 아이가 찾아먹내요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>26.02.07.</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>sook****</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>피로회복, 에너지 재주문 의사 있습니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>26.02.11.</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>pray********</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>고1 딸램 오리지널로 오래 먹었는데 샤인머스캣 먹어보고 앞으로는 샤인으로 사달라고 하네요~~새로운맛 제품 출시 좋으네요</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>26.02.03.</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>kaem****</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>졸릴때마다 효과좋아서 집중력흐려질때 좋대요</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>26.01.11.</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>lees********</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>기존에 먹고있었는데
+다떨어져서  구매할려니 샤인머스켓맛이 나와서
+2개 1개 조합으로 구매했어요
+저희아인  기존꺼는 새콤해서 샤인이 더 낫다고 합니다^^
+졸리지않아 시험기간
+방학때 먹어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>26.01.13.</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>kuku*****</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>타브랜드먹다 이번에 처음 먹여봤어요.
+아이 시험기간에도 먹고 남편 피곤할때도 먹는데 먹은날 컨디션이 더 좋았다고하네요.
+너무 피곤한날은 잘 모르겠다고하구요ㅎㅎ
+ 꾸준히먹는건아니고 필요에따라 보조적으로 먹고있어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>26.01.16.</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>only***</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>효과가 있는 것 같아서 여러번 구매하고 있어요. 젤리 형태인데 맛은 참고 먹게 됩니다. 오렌지 맛만 구매하다가 샤인머스캣 맛을 처음으로 구매해 봤는데 조금 더 나은 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>26.02.22.</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>came*****</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>아이가 사달라고해서 사줬는데 효과 있다고 합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>26.02.01.</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>babo***</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>좋은구성 만족합니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>26.02.15.</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>rtn0***</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>아이가 피곤해하고 시험볼때 집중을 위해 먹이고 있어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>26.01.06.</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>ok****</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>예비고등 아이가 피곤하면 찾아서 계속 재구매하게되내요. 샤인맛은 처음사봤는데 새콤달콤한 젤리처럼 맛있고 복용도 간편해서 너무좋아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>26.01.18.</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>1k****</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>샤인맛이 더 맛있다고 하네요. 시험기간에 주로 먹고 있어요.  다음에 샤인맛으로 다 구매해야겠어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>26.01.30.</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>we****</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>집중력을 위해서 사 봤어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>26.01.10.</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>pray********</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>고1 인데 다른거 여러개 먹어보고
+에너씨슬만 먹어요
+샤인머스캣 새로 나와서 먹고 있는데
+맛있다고 하네요
+기존것도 맛있고 샤인도 맛있고
+계속 구매할 예정이에요</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>26.01.28.</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>3한달사용</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>inoe*****</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>피곤할 때 회사에서 하나씩 먹으면 되게 좋더라구요
+저는 더 말캉 ! 한 젤리를 더 좋아해서 살짝 그 부분은 아쉽습니다 근데 주변에 하나 주기 좋아요</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>26.01.22.</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>soul***</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>없음앙되는 필수템이라 꾸준히 주문해서 쟁여놓습니당^^</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>26.01.12.</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>is****</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>커피와 에너지 드링크를 자주 먹는 수험생을 위해 구매했어요. 도움이 되면 좋겠어요~</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>26.02.02.</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>flut*****</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>이모가 사서 아이 먹여보라고 줘서 하나 먹어봤는데 아이가 학원에서 단어 시험칠때 먹고 가서 집중하는데 효과 봤다고 주문 해달라고 해서 추가 주문합니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>26.01.20.</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>fa****</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>아이가 힘들때마다 먹고있는데 샤인머스켓 맛있다고하네요</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>26.01.24.</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>naye******</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>늘먹던거예요
+격일로먹고잇어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>26.01.19.</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>jina*****</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>먹기전이라 어떻지 모르겠으나 좋은후기보고 구매하였습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>26.01.26.</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>3한달사용</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>113l*****</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>아이가 좋다고 합니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>26.01.17.</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>hs****</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>매번 주문해서 먹고 있고 온가족이 좋아하네요</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>25.12.30.</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>euge****</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>고등학생 아이를 위해 구입했어요. 시험기간에 카페인이 들어있는 커피나 에너지드링크 말고 이걸 먹겠다고하던데 각성효과가 있는듯합니다. 특정시기에 적절히 활용하면 좋을것같아요</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>25.12.25.</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>comp****</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>고1 딸이 기말고사에 체력도 떨어지고 공부한다고 잠 깰려고 에너지 음료를 매일 마시는데 주변 고3 엄마에게 물어보니 이것 먹으면 정신이 말짱해진다고 해서 사줬더니 아이가 좋대요 진짜 정신이 말짱해진대요
+덕분에 이번 시험을 조뮤잘 본 것 같아요</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>26.01.19.</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>flow*******</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>고2 아들이 꾸준히먹고있어요~</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>26.01.12.</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>cher******</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>아이가 꾸준히 챙겨먹고 있어요 덜 피곤해하는거 같아요</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>26.01.24.</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>heer***</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>자주 이용하고 있어요 빠른배송까지 감사합니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>26.01.25.</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>zita****</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>너무 좋아요~커피 마시지 않고 집중력 확 끌어올려줘요~</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>26.01.11.</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>ultr**********</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>아이가 졸릴때 효과 있다고 해서
+구매하고 있습니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>26.01.29.</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>pooh******</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>진짜 잠이안오네요 신기신기</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>26.01.11.</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>jrki***</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>고3수험생 아이 필수품입니다
+이번에 샤인맛도 사봤는데 아이가 좋아하네요
+확실히 피곤함이 덜하다고 해서 꾸준히 먹일 생각입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>26.01.30.</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>kamg*****</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>고3 딸이 게속 주문해 달라고 하네요</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>26.01.25.</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>yj****</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>배송도 빠르고 좋아요 좋아요</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>26.01.29.</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>nath****</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>아이가 피로할때 젤 괜찮다고하네요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>26.01.28.</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>hope***</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>다 먹고 부족하여 재주문입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>25.12.12.</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>th****</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>고딩 아이들이 맛이 처음 접해보는 맛이라 잘 챙겨 먹지 않다가 학원수업준비 시험준비하면서 자꾸 챙기더라구요~
+카페인 음료보다 훨씬 효과 좋다하네요~</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>25.12.11.</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>sand******</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>시험기간에 먹으려고 구입했어요
+지난번에 먹고 조금 효과가있는지 재구입해달라해서 샀는데
+새로운 맛도 기대되네요
+살짝 가격이 비싼거 말고는 
+배송도 빠르고 좋습니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>25.12.05.</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>sans*****</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>고등학생 아이 기말고사 기간이라 주문했어요. 에너지음료는 너무 자극적이라 자주 먹기 좀 그래서 주문해줬는데 효과 좋다고 하네요 ㅎㅎ
+휴대하기도 너무 편하고 젤리 타입이라 먹기에도 부담없어서 아침에 하나씩 챙겨가서 먹는답니다. 
+이번에 나온 샤인머스캣 맛도 궁금해서 한번 사봤어요~</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>25.12.18.</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>habi****</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>먹으면 안졸리다길래 구입했어요. 샤인머스캣만 먹어봐서 두가지 맛으로 구입했는데 향만 다르고 맛은 비슷하다네요</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>25.12.19.</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>mk****</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>항상 아이가 시험기간에 먹는거라 구매 했습니다. 다 떨어졌는데 빠른배송 좋아요</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>26.01.20.</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>yej4***</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>아들이 먹고 있는데 피곤함이 사라진다고 합니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>26.01.21.</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>minb******</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>맛도 먹을 만 하고 효과 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>26.01.13.</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>4한달사용</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>habi****</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>아주 맛있거나하진 않아서 자주먹지는 않아요 필요할 때 먹이려고 두고 있어요</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>25.12.18.</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>rool***</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>커피대신 잘 먹어요 피곤하면
+2가지맛으로 살수 있어 더 좋아요</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>25.12.22.</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>flow*******</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>고2 수험생이라 도움이된다고하네요..
+두번째 주문이네요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>25.12.09.</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>dlsk***</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>아이가 시험기간에 먹으면 정신이 깨는것 같다고 추가 주문해요 새로운 맛 청포도향이 강하지는 않고 오렌지맛과 큰 차이가 없어서 오히려 좋다고 해요</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>25.12.09.</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>kuku*****</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>아이 시험기간이라 구매했어요.
+공x젤 먹이다가 처음 구매했는데 아이는 둘다 맛없긴 똑같다네요ㅋㅋ
+오늘부터 첫 시험인데 정신 빠짝 차려 좋은성적 받아오길요~</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>25.12.07.</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>1k****</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>배송 엄청 빠르네요. 공부하는데 효과 있어서 주문했어요.   카페인 음료 마시는것 보다 건강에 더 좋아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>25.12.14.</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>khg9***</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>고등딸 항상 챙겨먹고있습니다 이번에 기말고사대비로 3박스 주문완료요 감사합니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>25.12.17.</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>tjsa*****</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>중딩 아들이 시험기간에 유용하게 잘 먹었습니다. 샤인머스컷 맛보다 기본맛이 더 좋다고 하네요</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>25.12.06.</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>inoe*****</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>종류별로 구매했는데 주황색이 제일 맛있어요 유학에 디자인이  화장품 브랜드 따라한 거 같은 느낌
+집중이 되는지 잘 모르겠어요^^; 더 오래 먹어야 되나요!</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>26.01.17.</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>clar*****</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>아이가 잘 먹어요....</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>26.01.11.</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>5한달사용</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>dlfl*******</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>새로나온 맛이 맛있다고 합니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>25.12.15.</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>choy***</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>아이가 원해서 사줬어요.
+맛있다고 잘 먹어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>25.12.07.</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>phk8***</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>고등아아가시험기간에  잘 이용하고있어요.천연이라 믿고 먹여요</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>25.12.03.</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>crys******</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>고등학생 딸아이가 항상 찾아서 언제나 쟁여놔요.
+카페인 들어간 음료보다 맛도 있고 훨씬 나은거같아요~</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>25.12.20.</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>clar*****</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>아이가 잘 먹습니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>25.12.03.</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>shin*****</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>피곤이 덜 한거 같아요.
+잘 먹고 있습니다.
+다 먹고 재구매 예정입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>25.12.02.</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>safe******</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>고딩학생 딸 주려고 샀어요!
+친구들 먹을때 얻어먹어봤는데 좋다고 하네요</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>25.11.28.</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>xenn*****</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>아이가 필요하다고 해서 또 주문했어요.
+시험 준비 기간이라 먹으면 효과가
+좋다고 하네요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>25.12.01.</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>babo***</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>엄청빠른 배송 감사합니다~
+아이가 찾아서 주문했어요~~</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>25.12.09.</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>113l*****</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>시험기간이라 재구매합니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>25.12.09.</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>dlfl*******</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>새로나온 맛 기대하고 주문했는데 아이가 너무 만족스러워ㅓ 하네요 세개 모두 샤인먼스켓 맛으로 구매할껄 후회중입니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>25.11.30.</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>co****</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>아이가 시험기간만 찾네요~ 먹으면 효과가 있다고해요~</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>25.12.16.</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>km****</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>집중이 잘되고 좋은거 같아요</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>25.11.29.</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>ohj4***</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>먹기 편하고  효과도 좋고  빠른 배송  만족합니다</t>
         </is>
       </c>
     </row>
